--- a/public/templates/forms/A-127-CertificateInventory-FORM.xlsx
+++ b/public/templates/forms/A-127-CertificateInventory-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Register!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -196,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -261,6 +266,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -644,7 +652,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="50.5" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Cert ID</t>
@@ -832,7 +840,6 @@
       <c r="B24" s="25" t="n"/>
       <c r="C24" s="13">
         <f>COUNTA(A12:A21)</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -844,7 +851,6 @@
       <c r="B25" s="25" t="n"/>
       <c r="C25" s="13">
         <f>COUNTIFS(F12:F21,"&gt;="&amp;TODAY(),F12:F21,"&lt;="&amp;(TODAY()+30))</f>
-        <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -856,7 +862,6 @@
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="13">
         <f>COUNTIFS(F12:F21,"&gt;="&amp;TODAY(),F12:F21,"&lt;="&amp;(TODAY()+60))</f>
-        <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -868,7 +873,6 @@
       <c r="B27" s="25" t="n"/>
       <c r="C27" s="13">
         <f>COUNTIF(D12:D21,"*self-signed*")</f>
-        <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -880,7 +884,6 @@
       <c r="B28" s="25" t="n"/>
       <c r="C28" s="13">
         <f>COUNTIF(J12:J21,"None")</f>
-        <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
@@ -892,7 +895,6 @@
       <c r="B29" s="25" t="n"/>
       <c r="C29" s="13">
         <f>COUNTIF(F12:F21,"&lt;"&amp;TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
@@ -1038,7 +1040,7 @@
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="12" t="n"/>
     </row>
-    <row r="47" ht="30" customHeight="1">
+    <row r="47" ht="66.4" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Drafter's note (internal, delete before publishing): single-sheet certificate register keyed to the Master Asset Inventory; self-signed certs recorded as approved exceptions (col H), DR availability tracked (col J) for continuity. Governed by the Key &amp; Certificate Management Policy; renewal and revocation are carried out under the Certificate Renewal &amp; Revocation Procedures. No CJIS or Indiana citation: State-maintained IDACS cryptography is out of PSAP scope (add CJIS §5.10.1.2 and 240 IAC 5 only if the agency manages certificates that protect CJI). Agency-supplied values in brackets.</t>
@@ -1078,14 +1080,18 @@
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="E12:E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Status" prompt="Select a status" type="list">
       <formula1>"Active,Under Review,Retired,Decommissioned"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation sqref="D12:D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Type (public CA / internal CA / " prompt="Select a value" type="list">
+      <formula1>"Public CA,Internal CA,Self-signed"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1093,7 +1099,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
@@ -1111,14 +1117,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="43.5" customHeight="1">
+    <row r="2" ht="161.4" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>How to use this template: fill the header block on the Register tab, replace every [BRACKETED] field, list one row per in-scope system or endpoint group, then delete every « » note before publishing.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="129.7" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, Source Authority, signatures and revision history live on the Register tab.</t>
@@ -1176,7 +1182,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="34.7" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Subject / System</t>
@@ -1220,7 +1226,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="50.5" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Type (public CA / internal CA / self-signed)</t>
@@ -1258,13 +1264,11 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+      <c r="D11" s="26">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Expiration Date</t>
@@ -1280,13 +1284,11 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>2027-01-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
+      <c r="D12" s="26">
+        <v>46402</v>
+      </c>
+    </row>
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Days to Expiry / Renewal Trigger</t>
@@ -1308,7 +1310,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Self-signed Exception (justification)</t>
@@ -1330,7 +1332,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="29.75" customHeight="1">
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Owner (Role)</t>
@@ -1352,7 +1354,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
           <t>DR Availability</t>
@@ -1377,7 +1379,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="18" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="133.7" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
           <t>« Certificates from a public or internal CA are tracked to renewal; self-signed certificates are recorded as approved exceptions with a justification. Keep each private key available for DR. »</t>
@@ -1396,7 +1398,7 @@
       </c>
       <c r="B20" s="21" t="n"/>
     </row>
-    <row r="21" ht="42" customHeight="1">
+    <row r="21" ht="104.6" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
           <t>What minimum-viable upkeep looks like at each PSAP size. Keep all three rows while this ships as a template; once adopted, keep the one that fits.</t>
@@ -1416,7 +1418,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="66.4" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Small (1–5, no in-house IT)</t>
@@ -1428,7 +1430,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="50.5" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Medium (6–25, shared county IT)</t>
@@ -1440,7 +1442,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="66.4" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Large (25+, dedicated IT/security)</t>
@@ -1454,6 +1456,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>